--- a/artfynd/A 12490-2026 artfynd.xlsx
+++ b/artfynd/A 12490-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>64622642</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +778,561 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>64622526</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gullberget V om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>518624</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6691916</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-03-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-03-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera tjädertallar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104886676</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SKOG OCH MYR SSV om Borlänge tätort. Gullberget, Klackberget m.m, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>518626</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104886678</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SKOG OCH MYR SSV om Borlänge tätort. Gullberget, Klackberget m.m, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518745</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691984</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104888606</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SKOG OCH MYR SSV om Borlänge tätort. Gullberget, Klackberget m.m, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518565</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-03-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104888607</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SKOG OCH MYR SSV om Borlänge tätort. Gullberget, Klackberget m.m, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>518508</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6692059</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-03-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12490-2026 artfynd.xlsx
+++ b/artfynd/A 12490-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64622642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64622526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104886676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104886678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104888606</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,8 +1362,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104888607</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>